--- a/tests/data/test_viemaritiedot/viemari_otsikkovirhe.xlsx
+++ b/tests/data/test_viemaritiedot/viemari_otsikkovirhe.xlsx
@@ -158,11 +158,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1014" style="0" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -172,17 +173,6 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="n">
